--- a/r4-ELGA-e-Medikation-ballot_2026_03/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
+++ b/r4-ELGA-e-Medikation-ballot_2026_03/StructureDefinition-at-elga-emed-device-fachanwendung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T15:54:42+00:00</t>
+    <t>2026-10-29T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
